--- a/spatial_data/grids/ten arcminute grid polys shore METADATA.xlsx
+++ b/spatial_data/grids/ten arcminute grid polys shore METADATA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/blake.feist/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/blake.feist/Documents/GitHub/VMS-pipeline/spatial_data/grids/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B63CD9D-7AFE-3F41-BB52-0DF620816A0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA538339-A4A6-C141-8B0A-147B8C3665CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" activeTab="1" xr2:uid="{AD14FED6-09D0-AC4E-9FD4-5D358E8F4B1E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="118">
   <si>
     <t>Shoreline</t>
   </si>
@@ -360,12 +360,52 @@
   </si>
   <si>
     <t>If this value is &gt;1, then it corresponds to a group of 10-arcminute grid cells. BLOCK10_n = 1 is a single 10-arcminute grid cell, but those &gt;=3 (there aren't any with a count = 2) should be grouped accordingly when joining to fish tickets. For example, 9, 10-arcminute grid cells will have a BLOCK10_ID = 138, so a fish ticket listing CDFW_AREA_BLOCK = 138 will be attributed to 9 grid cells, so the value of each of those 9 grid cells should be multiplied by 1/9.</t>
+  </si>
+  <si>
+    <t>Last updated:</t>
+  </si>
+  <si>
+    <t>Majority; 100%</t>
+  </si>
+  <si>
+    <t>Zone 1
+Zone 2
+Zone 2 &amp; Zone 7
+Zone 3 &amp; Zone 7
+Zone 4
+Zone 4 &amp; Zone 7
+Zone 5
+Zone 6</t>
+  </si>
+  <si>
+    <t>Zone 7 (sea turtles) overlaps with Zones 2, 3 and 4. To filter out Zone 7 from these zones, combine Zone 2 with Zone 2 &amp; Zone 7 (Zone 2); Zone 3 &amp; Zone 7 is just Zone 3; and, combine Zone 4 with Zone 4 &amp; Zone 7 (Zone 4)</t>
+  </si>
+  <si>
+    <t>CDFW (2023) Risk Assessment and Mitigation Program (RAMP) Fishing Zones - R7 - CDFW [ds3120]. URL: https://data-cdfw.opendata.arcgis.com/datasets/CDFW::risk-assessment-and-mitigation-program-ramp-fishing-zones-r7-cdfw-ds3120/about. Accessed 7 April 2025</t>
+  </si>
+  <si>
+    <t>Risk Assessment and Mitigation Program (RAMP) Fishing Zone (R7 - CDFW) that centroid of 10-arcminute grid cell falls within</t>
+  </si>
+  <si>
+    <t>RAMP_zone</t>
+  </si>
+  <si>
+    <t>RAMP_over</t>
+  </si>
+  <si>
+    <t>Proportion of 10-arcminute grid cell that falls within given RAMP zone</t>
+  </si>
+  <si>
+    <t>Not all RAMP zone latitudinal boundaries are at multiples of 10-arcminutes, so some 10-arcminute grid cells are not fully within the listed RAMP zone. 10-arcminute grid cells with "majority" attribute do not share a common border with the associated RAMP zone. However, the majority of the area of that grid cell falls within the corresponding RAMP zone.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yyyy;@"/>
+  </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -417,7 +457,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -436,6 +476,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -751,7 +794,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16BD5892-78CC-4C4F-B680-CA55ABBA4CB7}">
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="21" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.33203125" style="6" bestFit="1" customWidth="1"/>
@@ -768,136 +811,144 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B2" s="7">
+        <v>45919</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="102" x14ac:dyDescent="0.2">
-      <c r="A3" s="6" t="s">
+    <row r="4" spans="1:2" ht="102" x14ac:dyDescent="0.2">
+      <c r="A4" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B4" s="3" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B5" t="s">
         <v>96</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B5" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="6" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B10" s="2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B10" s="2" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B11" s="2" t="s">
         <v>51</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B12" s="2" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B18" s="2" t="s">
         <v>45</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B19" s="2" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B27" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="51" x14ac:dyDescent="0.2">
-      <c r="A27" s="6" t="s">
+    <row r="28" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="A28" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B28" s="3" t="s">
         <v>60</v>
       </c>
     </row>
@@ -908,13 +959,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D9FB08F-BEF6-184B-A396-B1BC5FCCFD71}">
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="95.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="78" style="1" customWidth="1"/>
     <col min="3" max="3" width="13.6640625" customWidth="1"/>
-    <col min="4" max="4" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="40.1640625" style="1" customWidth="1"/>
     <col min="5" max="5" width="58.6640625" style="1" customWidth="1"/>
     <col min="6" max="6" width="120.83203125" style="1" customWidth="1"/>
   </cols>
@@ -929,7 +980,7 @@
       <c r="C1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>12</v>
       </c>
       <c r="E1" s="5" t="s">
@@ -949,7 +1000,7 @@
       <c r="C2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E2" s="3"/>
@@ -965,6 +1016,7 @@
       <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
     </row>
@@ -978,6 +1030,7 @@
       <c r="C4" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
     </row>
@@ -988,6 +1041,7 @@
       <c r="B5" s="3" t="s">
         <v>82</v>
       </c>
+      <c r="D5" s="3"/>
       <c r="E5" s="3" t="s">
         <v>102</v>
       </c>
@@ -1005,9 +1059,10 @@
       <c r="C6" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="D6" s="3"/>
       <c r="E6" s="3"/>
     </row>
-    <row r="7" spans="1:6" s="2" customFormat="1" ht="102" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" s="2" customFormat="1" ht="68" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
@@ -1017,7 +1072,7 @@
       <c r="C7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E7" s="3" t="s">
@@ -1027,7 +1082,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:6" s="2" customFormat="1" ht="102" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" s="2" customFormat="1" ht="68" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>68</v>
       </c>
@@ -1037,7 +1092,7 @@
       <c r="C8" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E8" s="3" t="s">
@@ -1045,7 +1100,7 @@
       </c>
       <c r="F8" s="3"/>
     </row>
-    <row r="9" spans="1:6" s="2" customFormat="1" ht="102" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" s="2" customFormat="1" ht="68" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>9</v>
       </c>
@@ -1055,6 +1110,7 @@
       <c r="C9" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="D9" s="3"/>
       <c r="E9" s="3" t="s">
         <v>63</v>
       </c>
@@ -1070,6 +1126,7 @@
       <c r="C10" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="D10" s="3"/>
       <c r="E10" s="3" t="s">
         <v>105</v>
       </c>
@@ -1085,6 +1142,7 @@
       <c r="C11" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="D11" s="3"/>
       <c r="E11" s="3" t="s">
         <v>107</v>
       </c>
@@ -1102,6 +1160,7 @@
       <c r="C12" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="D12" s="3"/>
       <c r="E12" s="3" t="s">
         <v>103</v>
       </c>
@@ -1119,6 +1178,7 @@
       <c r="C13" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="D13" s="3"/>
       <c r="F13" s="3" t="s">
         <v>34</v>
       </c>
@@ -1133,6 +1193,7 @@
       <c r="C14" s="2" t="s">
         <v>19</v>
       </c>
+      <c r="D14" s="3"/>
       <c r="F14" s="3" t="s">
         <v>34</v>
       </c>
@@ -1147,6 +1208,7 @@
       <c r="C15" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3" t="s">
         <v>34</v>
@@ -1162,6 +1224,7 @@
       <c r="C16" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="D16" s="3"/>
       <c r="F16" s="3" t="s">
         <v>34</v>
       </c>
@@ -1208,6 +1271,7 @@
       <c r="C19" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3" t="s">
         <v>34</v>
@@ -1251,6 +1315,7 @@
       <c r="C22" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
     </row>
@@ -1264,6 +1329,7 @@
       <c r="C23" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
     </row>
@@ -1277,6 +1343,7 @@
       <c r="C24" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="D24" s="3"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
     </row>
@@ -1290,6 +1357,7 @@
       <c r="C25" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
     </row>
@@ -1303,6 +1371,7 @@
       <c r="C26" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="D26" s="3"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
     </row>
@@ -1316,6 +1385,7 @@
       <c r="C27" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="D27" s="3"/>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
     </row>
@@ -1329,8 +1399,72 @@
       <c r="C28" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="D28" s="3"/>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
+    </row>
+    <row r="29" spans="1:6" s="2" customFormat="1" ht="136" x14ac:dyDescent="0.2">
+      <c r="A29" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" s="2" customFormat="1" ht="102" x14ac:dyDescent="0.2">
+      <c r="A30" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="F30" s="3"/>
+    </row>
+    <row r="31" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+    </row>
+    <row r="33" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+    </row>
+    <row r="34" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+    </row>
+    <row r="35" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/spatial_data/grids/ten arcminute grid polys shore METADATA.xlsx
+++ b/spatial_data/grids/ten arcminute grid polys shore METADATA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/blake.feist/Documents/GitHub/VMS-pipeline/spatial_data/grids/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA538339-A4A6-C141-8B0A-147B8C3665CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B50B00AD-887F-B14D-9DE8-E8EDCE6E373A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" activeTab="1" xr2:uid="{AD14FED6-09D0-AC4E-9FD4-5D358E8F4B1E}"/>
   </bookViews>
@@ -113,9 +113,6 @@
     <t>Weighted mean depth of grid cell based on Feist et al. bathymetry</t>
   </si>
   <si>
-    <t>Number of Feist et al. bathymetry grid cells within 5km grid cell</t>
-  </si>
-  <si>
     <t>Median depth of grid cell based on Feist et al. bathymetry</t>
   </si>
   <si>
@@ -398,13 +395,16 @@
   <si>
     <t>Not all RAMP zone latitudinal boundaries are at multiples of 10-arcminutes, so some 10-arcminute grid cells are not fully within the listed RAMP zone. 10-arcminute grid cells with "majority" attribute do not share a common border with the associated RAMP zone. However, the majority of the area of that grid cell falls within the corresponding RAMP zone.</t>
   </si>
+  <si>
+    <t>Number of Feist et al. bathymetry grid cells within grid cell</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yyyy;@"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -477,7 +477,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -803,15 +803,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B2" s="7">
         <v>45919</v>
@@ -819,137 +819,137 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="102" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="51" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -995,7 +995,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>18</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="3" spans="1:6" s="2" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>13</v>
@@ -1022,10 +1022,10 @@
     </row>
     <row r="4" spans="1:6" s="2" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>23</v>
@@ -1036,25 +1036,25 @@
     </row>
     <row r="5" spans="1:6" s="2" customFormat="1" ht="85" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" s="2" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" s="2" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>23</v>
@@ -1067,7 +1067,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>19</v>
@@ -1076,7 +1076,7 @@
         <v>17</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>22</v>
@@ -1084,10 +1084,10 @@
     </row>
     <row r="8" spans="1:6" s="2" customFormat="1" ht="68" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>19</v>
@@ -1096,7 +1096,7 @@
         <v>16</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F8" s="3"/>
     </row>
@@ -1105,67 +1105,67 @@
         <v>9</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F9" s="3"/>
     </row>
-    <row r="10" spans="1:6" s="2" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" s="2" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F10" s="3"/>
     </row>
     <row r="11" spans="1:6" s="2" customFormat="1" ht="136" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:6" s="2" customFormat="1" ht="85" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:6" s="2" customFormat="1" ht="34" x14ac:dyDescent="0.2">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="D13" s="3"/>
       <c r="F13" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="2" customFormat="1" ht="34" x14ac:dyDescent="0.2">
@@ -1188,14 +1188,14 @@
         <v>2</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>25</v>
+        <v>117</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D14" s="3"/>
       <c r="F14" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:6" s="2" customFormat="1" ht="34" x14ac:dyDescent="0.2">
@@ -1203,7 +1203,7 @@
         <v>3</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>23</v>
@@ -1211,7 +1211,7 @@
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:6" s="2" customFormat="1" ht="34" x14ac:dyDescent="0.2">
@@ -1219,14 +1219,14 @@
         <v>4</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D16" s="3"/>
       <c r="F16" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:6" s="2" customFormat="1" ht="34" x14ac:dyDescent="0.2">
@@ -1234,7 +1234,7 @@
         <v>5</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>23</v>
@@ -1242,7 +1242,7 @@
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:6" s="2" customFormat="1" ht="34" x14ac:dyDescent="0.2">
@@ -1250,7 +1250,7 @@
         <v>6</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>23</v>
@@ -1258,7 +1258,7 @@
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:6" s="2" customFormat="1" ht="34" x14ac:dyDescent="0.2">
@@ -1266,7 +1266,7 @@
         <v>7</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>23</v>
@@ -1274,18 +1274,18 @@
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:6" s="2" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
@@ -1293,10 +1293,10 @@
     </row>
     <row r="21" spans="1:6" s="2" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>13</v>
@@ -1307,10 +1307,10 @@
     </row>
     <row r="22" spans="1:6" s="2" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>13</v>
@@ -1321,10 +1321,10 @@
     </row>
     <row r="23" spans="1:6" s="2" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>13</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="24" spans="1:6" s="2" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>13</v>
@@ -1349,10 +1349,10 @@
     </row>
     <row r="25" spans="1:6" s="2" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>13</v>
@@ -1363,10 +1363,10 @@
     </row>
     <row r="26" spans="1:6" s="2" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>13</v>
@@ -1377,10 +1377,10 @@
     </row>
     <row r="27" spans="1:6" s="2" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>13</v>
@@ -1391,10 +1391,10 @@
     </row>
     <row r="28" spans="1:6" s="2" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>13</v>
@@ -1405,39 +1405,39 @@
     </row>
     <row r="29" spans="1:6" s="2" customFormat="1" ht="136" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D29" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E29" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="F29" s="3" t="s">
         <v>111</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="30" spans="1:6" s="2" customFormat="1" ht="102" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F30" s="3"/>
     </row>
